--- a/Files/Scenarios.xlsx
+++ b/Files/Scenarios.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
   <si>
     <t>Scenarios</t>
   </si>
@@ -45,6 +46,15 @@
   </si>
   <si>
     <t>Add Candidate</t>
+  </si>
+  <si>
+    <t>Add Product To Wishlist</t>
+  </si>
+  <si>
+    <t>Add Product to Cart</t>
+  </si>
+  <si>
+    <t>Order an Item</t>
   </si>
 </sst>
 </file>
@@ -1046,4 +1056,52 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="22.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="12.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>